--- a/artfynd/A 62800-2023 artfynd.xlsx
+++ b/artfynd/A 62800-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62800-2023 artfynd.xlsx
+++ b/artfynd/A 62800-2023 artfynd.xlsx
@@ -6435,10 +6435,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119558933</v>
+        <v>119558932</v>
       </c>
       <c r="B52" t="n">
-        <v>91886</v>
+        <v>89633</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119558932</v>
+        <v>119558933</v>
       </c>
       <c r="B53" t="n">
-        <v>89633</v>
+        <v>91886</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6562,25 +6562,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 62800-2023 artfynd.xlsx
+++ b/artfynd/A 62800-2023 artfynd.xlsx
@@ -6435,10 +6435,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119558932</v>
+        <v>119558933</v>
       </c>
       <c r="B52" t="n">
-        <v>89633</v>
+        <v>91886</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1962</v>
+        <v>232140</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6550,10 +6550,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119558933</v>
+        <v>119558932</v>
       </c>
       <c r="B53" t="n">
-        <v>91886</v>
+        <v>89633</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6562,25 +6562,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 62800-2023 artfynd.xlsx
+++ b/artfynd/A 62800-2023 artfynd.xlsx
@@ -6438,7 +6438,7 @@
         <v>119558933</v>
       </c>
       <c r="B52" t="n">
-        <v>91886</v>
+        <v>92319</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6447,25 +6447,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>232140</v>
+        <v>5448</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6532,18 +6532,19 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan  Tyrén</t>
+          <t>Håkan Tyrén</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>

--- a/artfynd/A 62800-2023 artfynd.xlsx
+++ b/artfynd/A 62800-2023 artfynd.xlsx
@@ -6438,7 +6438,7 @@
         <v>119558933</v>
       </c>
       <c r="B52" t="n">
-        <v>92319</v>
+        <v>92474</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
